--- a/scripts/checks/results/HLR_results_02_Dunn_fams_tPBC.xlsx
+++ b/scripts/checks/results/HLR_results_02_Dunn_fams_tPBC.xlsx
@@ -553,66 +553,66 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>539</v>
+        <v>662</v>
       </c>
       <c r="E2" t="n">
-        <v>537</v>
+        <v>660</v>
       </c>
       <c r="F2" t="n">
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3002424530370029</v>
+        <v>0.2235251913827403</v>
       </c>
       <c r="H2" t="n">
-        <v>230.4086579424865</v>
+        <v>189.9953799857627</v>
       </c>
       <c r="I2" t="n">
-        <v>1.460779915114385e-43</v>
+        <v>3.606805372741333e-38</v>
       </c>
       <c r="J2" t="n">
-        <v>71.15456703886447</v>
+        <v>91.34369889831773</v>
       </c>
       <c r="K2" t="n">
-        <v>101.6846011131726</v>
+        <v>117.6389728096677</v>
       </c>
       <c r="L2" t="n">
-        <v>30.53003407430809</v>
+        <v>26.29527391134995</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1325038492343845</v>
+        <v>0.1383995437853299</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1890048347828486</v>
+        <v>0.1779712145380752</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>{'const': 0.8158622228498638, 'N1ratio-ArgsPreds': -0.23974231781280247}</t>
+          <t>{'const': 0.6122542310653039, 'N1ratio-ArgsPreds': -2.3586335149019666}</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>{'const': 3.861723678139761e-68, 'N1ratio-ArgsPreds': 1.4607799151140621e-43}</t>
+          <t>{'const': 7.046203500856338e-68, 'N1ratio-ArgsPreds': 3.606805372740735e-38}</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.5479438411342928}</t>
+          <t>{'N1ratio-ArgsPreds': -0.47278450839969377}</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.5479438411342936)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4727845083996953)}</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.5479438411342935)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4727845083996953)}</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(30.024245303700386)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(22.352519138274157)}</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -628,80 +628,80 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>['N1ratio-ArgsPreds', 'latitude', 'longitude', 'Macro_class']</t>
+          <t>['N1ratio-ArgsPreds', 'Macro_class']</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>539</v>
+        <v>662</v>
       </c>
       <c r="E3" t="n">
-        <v>534</v>
+        <v>659</v>
       </c>
       <c r="F3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4282747392666378</v>
+        <v>0.3560262910941564</v>
       </c>
       <c r="H3" t="n">
-        <v>100.0037633788599</v>
+        <v>182.1668513685808</v>
       </c>
       <c r="I3" t="n">
-        <v>1.702338642847579e-63</v>
+        <v>1.052085809153766e-63</v>
       </c>
       <c r="J3" t="n">
-        <v>58.13565508399651</v>
+        <v>75.75640563211539</v>
       </c>
       <c r="K3" t="n">
-        <v>101.6846011131726</v>
+        <v>117.6389728096677</v>
       </c>
       <c r="L3" t="n">
-        <v>10.88723650729401</v>
+        <v>20.94128358877614</v>
       </c>
       <c r="M3" t="n">
-        <v>0.108868267947559</v>
+        <v>0.1149566094569277</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1890048347828486</v>
+        <v>0.1779712145380752</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>{'const': 0.5707301483093369, 'N1ratio-ArgsPreds': -0.23736630054157704, 'latitude': 0.004125113705238998, 'longitude': 0.0003535003417894755, 'Macro_class': 0.07277894332771967}</t>
+          <t>{'const': 0.3619998855036547, 'N1ratio-ArgsPreds': -2.2027437971292594, 'Macro_class': 0.09112675272855822}</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>{'const': 4.590399335908072e-33, 'N1ratio-ArgsPreds': 6.126742452179407e-49, 'latitude': 5.991196955199697e-07, 'longitude': 0.16164137009314025, 'Macro_class': 9.880785720371535e-12}</t>
+          <t>{'const': 1.304818894091303e-22, 'N1ratio-ArgsPreds': 1.6087074029134122e-39, 'Macro_class': 1.2538119742188098e-28}</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.5425133270637095, 'latitude': 0.18532462755220405, 'longitude': 0.05907319878123149, 'Macro_class': 0.2765293156965464}</t>
+          <t>{'N1ratio-ArgsPreds': -0.44153665106362106, 'Macro_class': 0.3653457654052022}</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.5772079889797707), 'latitude': np.float64(0.21360542253202497), 'longitude': np.float64(0.06053820186776226), 'Macro_class': np.float64(0.2884699120894178)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4807058994073272), 'Macro_class': np.float64(0.4130913073140003)}</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.534463625943419), 'latitude': np.float64(0.16532820660595793), 'longitude': np.float64(0.04585856776705677), 'Macro_class': np.float64(0.2278035235834368)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.43991869944543266), 'Macro_class': np.float64(0.3640070050306952)}</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(28.56513674565869), 'latitude': np.float64(2.733341589954231), 'longitude': np.float64(0.21030082376457382), 'Macro_class': np.float64(5.189444535702945)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(19.352846212176093), 'Macro_class': np.float64(13.250109971141658)}</t>
         </is>
       </c>
       <c r="U3" t="n">
-        <v>0.1280322862296349</v>
+        <v>0.1325010997114161</v>
       </c>
       <c r="V3" t="n">
-        <v>39.86136089149219</v>
+        <v>135.5928409844293</v>
       </c>
       <c r="W3" t="n">
-        <v>2.945126212213881e-23</v>
+        <v>1.253811974219762e-28</v>
       </c>
     </row>
     <row r="4">
@@ -713,80 +713,80 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>['N1ratio-ArgsPreds', 'latitude', 'longitude', 'Macro_class', 'Fam_class']</t>
+          <t>['N1ratio-ArgsPreds', 'Macro_class', 'Fam_class']</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>539</v>
+        <v>662</v>
       </c>
       <c r="E4" t="n">
-        <v>533</v>
+        <v>658</v>
       </c>
       <c r="F4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4308967329877673</v>
+        <v>0.3574609078035639</v>
       </c>
       <c r="H4" t="n">
-        <v>80.71222640777542</v>
+        <v>122.020735231695</v>
       </c>
       <c r="I4" t="n">
-        <v>5.384584677552259e-63</v>
+        <v>7.732030001274338e-63</v>
       </c>
       <c r="J4" t="n">
-        <v>57.86903869834222</v>
+        <v>75.5876387960451</v>
       </c>
       <c r="K4" t="n">
-        <v>101.6846011131726</v>
+        <v>117.6389728096677</v>
       </c>
       <c r="L4" t="n">
-        <v>8.763112482966068</v>
+        <v>14.01711133787419</v>
       </c>
       <c r="M4" t="n">
-        <v>0.108572305250173</v>
+        <v>0.114874830997029</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1890048347828486</v>
+        <v>0.1779712145380752</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>{'const': 0.6961464576636499, 'N1ratio-ArgsPreds': -0.234080535081691, 'latitude': 0.003932715362527422, 'longitude': -6.492392921279064e-05, 'Macro_class': 0.058273569555529196, 'Fam_class': -0.0017571297445560055}</t>
+          <t>{'const': 0.4270272555566415, 'N1ratio-ArgsPreds': -2.195768543817306, 'Macro_class': 0.0783461168014444, 'Fam_class': -0.0008073176147426613}</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>{'const': 1.285483155206823e-13, 'N1ratio-ArgsPreds': 3.5622512818011976e-47, 'latitude': 2.3833674210851503e-06, 'longitude': 0.8596779117771504, 'Macro_class': 3.455875400858192e-05, 'Fam_class': 0.11769560292191579}</t>
+          <t>{'const': 6.983427455999342e-11, 'N1ratio-ArgsPreds': 2.7849527092732195e-39, 'Macro_class': 3.944167911357278e-09, 'Fam_class': 0.22591698885923128}</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.5350035350354112, 'latitude': 0.17668095037079692, 'longitude': -0.010849393119766336, 'Macro_class': 0.22141500790721202, 'Fam_class': -0.11935728648818478}</t>
+          <t>{'N1ratio-ArgsPreds': -0.44013847212347645, 'Macro_class': 0.31410558537744077, 'Fam_class': -0.0638308925158155}</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.5687521701925946), 'latitude': np.float64(0.20233083487677564), 'longitude': np.float64(-0.007660853127783767), 'Macro_class': np.float64(0.1780213224686194), 'Fam_class': np.float64(-0.06772080829358151)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.47969635395302423), 'Macro_class': np.float64(0.22657552294544023), 'Fam_class': np.float64(-0.04719911699693482)}</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.5216485146302986), 'latitude': np.float64(0.15585983719914648), 'longitude': np.float64(-0.005779435483898172), 'Macro_class': np.float64(0.13647739071120824), 'Fam_class': np.float64(-0.05120540714737771)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4382293480554767), 'Macro_class': np.float64(0.18646901023729165), 'Fam_class': np.float64(-0.03787633442411308)}</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(27.211717281599686), 'latitude': np.float64(2.4292288851744446), 'longitude': np.float64(0.0033401874512541297), 'Macro_class': np.float64(1.8626078175339789), 'Fam_class': np.float64(0.26219937211287203)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(19.204496149712813), 'Macro_class': np.float64(3.477069177887518), 'Fam_class': np.float64(0.14346167094072537)}</t>
         </is>
       </c>
       <c r="U4" t="n">
-        <v>0.002621993721129479</v>
+        <v>0.001434616709407477</v>
       </c>
       <c r="V4" t="n">
-        <v>2.455657407659853</v>
+        <v>1.469136751762846</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1176956029219286</v>
+        <v>0.2259169888597093</v>
       </c>
     </row>
     <row r="5">
@@ -798,80 +798,80 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>['N1ratio-ArgsPreds', 'latitude', 'longitude', 'Macro_class', 'Fam_class', 'Nlen_freq', 'Vlen_freq']</t>
+          <t>['N1ratio-ArgsPreds', 'Macro_class', 'Fam_class', 'Nlen_freq', 'Vlen_freq']</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>539</v>
+        <v>662</v>
       </c>
       <c r="E5" t="n">
-        <v>531</v>
+        <v>656</v>
       </c>
       <c r="F5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4605058979068151</v>
+        <v>0.3855974616497843</v>
       </c>
       <c r="H5" t="n">
-        <v>64.75077586305163</v>
+        <v>82.34078443799439</v>
       </c>
       <c r="I5" t="n">
-        <v>3.55672114852878e-67</v>
+        <v>4.442106470941744e-67</v>
       </c>
       <c r="J5" t="n">
-        <v>54.85824257425471</v>
+        <v>72.27768350317183</v>
       </c>
       <c r="K5" t="n">
-        <v>101.6846011131726</v>
+        <v>117.6389728096677</v>
       </c>
       <c r="L5" t="n">
-        <v>6.689479791273979</v>
+        <v>9.072257861299169</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1033111912886153</v>
+        <v>0.1101793955841034</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1890048347828486</v>
+        <v>0.1779712145380752</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>{'const': 0.3013014345823354, 'N1ratio-ArgsPreds': -0.2187528504296818, 'latitude': 0.0038626991338975582, 'longitude': -0.0005816308890785551, 'Macro_class': 0.03965047136416332, 'Fam_class': -0.004469086952158804, 'Nlen_freq': 0.047799212071237, 'Vlen_freq': 0.03496604140457689}</t>
+          <t>{'const': 0.18015827901476222, 'N1ratio-ArgsPreds': -2.0797628700318627, 'Macro_class': 0.06845659271188595, 'Fam_class': -0.0018767080107924884, 'Nlen_freq': 0.28074866988727754, 'Vlen_freq': 0.5450644056063418}</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>{'const': 0.01167273354297994, 'N1ratio-ArgsPreds': 9.545059203789041e-42, 'latitude': 2.1179641117540256e-06, 'longitude': 0.11720723741364805, 'Macro_class': 0.005383749551475992, 'Fam_class': 0.0002506822457137312, 'Nlen_freq': 0.07177602002568405, 'Vlen_freq': 0.06612207205839887}</t>
+          <t>{'const': 0.022096224750886184, 'N1ratio-ArgsPreds': 7.7542481976178e-36, 'Macro_class': 2.890193153089037e-07, 'Fam_class': 0.0073492135949451975, 'Nlen_freq': 0.2386491733760133, 'Vlen_freq': 0.013544549634791955}</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.4999712950848697, 'latitude': 0.17353540520025776, 'longitude': -0.0971959375029516, 'Macro_class': 0.15065508252854065, 'Fam_class': -0.30357353709484436, 'Nlen_freq': 0.10205990338527482, 'Vlen_freq': 0.10161364849679277}</t>
+          <t>{'N1ratio-ArgsPreds': -0.41688531087324054, 'Macro_class': 0.2744564632502061, 'Fam_class': -0.1483826750871153, 'Nlen_freq': 0.06147936684426154, 'Vlen_freq': 0.12586307125780943}</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.5404188496272267), 'latitude': np.float64(0.20371213287087744), 'longitude': np.float64(-0.06793824368417971), 'Macro_class': np.float64(0.12039455798165379), 'Fam_class': np.float64(-0.15797378583359561), 'Nlen_freq': np.float64(0.07805411206423138), 'Vlen_freq': np.float64(0.07965558414275081)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.46042737674513745), 'Macro_class': np.float64(0.19839239081483445), 'Fam_class': np.float64(-0.10441310382752554), 'Nlen_freq': np.float64(0.04600078536590982), 'Vlen_freq': np.float64(0.09621588418529682)}</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.4717623989193407), 'latitude': np.float64(0.15283185281610756), 'longitude': np.float64(-0.05001637956245846), 'Macro_class': np.float64(0.0890780616243271), 'Fam_class': np.float64(-0.11750766774176961), 'Nlen_freq': np.float64(0.057506394876072425), 'Vlen_freq': np.float64(0.05869373797906177)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.40655817977632014), 'Macro_class': np.float64(0.1586613242731975), 'Fam_class': np.float64(-0.08229280502384366), 'Nlen_freq': np.float64(0.03609538954692018), 'Vlen_freq': np.float64(0.07576923079862471)}</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(22.255976103413115), 'latitude': np.float64(2.3357575235204364), 'longitude': np.float64(0.25016382245359126), 'Macro_class': np.float64(0.7934901062747418), 'Fam_class': np.float64(1.3808051978110123), 'Nlen_freq': np.float64(0.3306985451642769), 'Vlen_freq': np.float64(0.34449548779547584)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(16.528955354303466), 'Macro_class': np.float64(2.5173415820124734), 'Fam_class': np.float64(0.6772105758692348), 'Nlen_freq': np.float64(0.13028771465439146), 'Vlen_freq': np.float64(0.574097633581526)}</t>
         </is>
       </c>
       <c r="U5" t="n">
-        <v>0.02960916491904775</v>
+        <v>0.02813655384622038</v>
       </c>
       <c r="V5" t="n">
-        <v>14.57149069008605</v>
+        <v>15.02075444925942</v>
       </c>
       <c r="W5" t="n">
-        <v>6.906177973554183e-07</v>
+        <v>4.183408356918239e-07</v>
       </c>
     </row>
   </sheetData>

--- a/scripts/checks/results/HLR_results_02_Dunn_fams_tPBC.xlsx
+++ b/scripts/checks/results/HLR_results_02_Dunn_fams_tPBC.xlsx
@@ -562,57 +562,57 @@
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2235251913827403</v>
+        <v>0.2127090200070492</v>
       </c>
       <c r="H2" t="n">
-        <v>189.9953799857627</v>
+        <v>178.3177462618833</v>
       </c>
       <c r="I2" t="n">
-        <v>3.606805372741333e-38</v>
+        <v>3.551046890077052e-36</v>
       </c>
       <c r="J2" t="n">
-        <v>91.34369889831773</v>
+        <v>92.1915359049147</v>
       </c>
       <c r="K2" t="n">
-        <v>117.6389728096677</v>
+        <v>117.0996978851963</v>
       </c>
       <c r="L2" t="n">
-        <v>26.29527391134995</v>
+        <v>24.90816198028165</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1383995437853299</v>
+        <v>0.1396841453104768</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1779712145380752</v>
+        <v>0.1771553674511291</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>{'const': 0.6122542310653039, 'N1ratio-ArgsPreds': -2.3586335149019666}</t>
+          <t>{'const': 0.5881292512992626, 'N1ratio-ArgsPreds': -2.1993804205042555}</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>{'const': 7.046203500856338e-68, 'N1ratio-ArgsPreds': 3.606805372740735e-38}</t>
+          <t>{'const': 5.747937176790004e-66, 'N1ratio-ArgsPreds': 3.551046890075819e-36}</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.47278450839969377}</t>
+          <t>{'N1ratio-ArgsPreds': -0.4612038811708435}</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.4727845083996953)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4612038811708424)}</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.4727845083996953)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.46120388117084227)}</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(22.352519138274157)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(21.27090200070484)}</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -641,67 +641,67 @@
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3560262910941564</v>
+        <v>0.3473212616629447</v>
       </c>
       <c r="H3" t="n">
-        <v>182.1668513685808</v>
+        <v>175.3425521559432</v>
       </c>
       <c r="I3" t="n">
-        <v>1.052085809153766e-63</v>
+        <v>8.779581860525752e-62</v>
       </c>
       <c r="J3" t="n">
-        <v>75.75640563211539</v>
+        <v>76.42848307536029</v>
       </c>
       <c r="K3" t="n">
-        <v>117.6389728096677</v>
+        <v>117.0996978851963</v>
       </c>
       <c r="L3" t="n">
-        <v>20.94128358877614</v>
+        <v>20.33560740491803</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1149566094569277</v>
+        <v>0.1159764538321097</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1779712145380752</v>
+        <v>0.1771553674511291</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>{'const': 0.3619998855036547, 'N1ratio-ArgsPreds': -2.2027437971292594, 'Macro_class': 0.09112675272855822}</t>
+          <t>{'const': 0.33575922902106625, 'N1ratio-ArgsPreds': -2.0402524425515702, 'Macro_class': 0.0916801161601071}</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>{'const': 1.304818894091303e-22, 'N1ratio-ArgsPreds': 1.6087074029134122e-39, 'Macro_class': 1.2538119742188098e-28}</t>
+          <t>{'const': 3.0514726730384744e-20, 'N1ratio-ArgsPreds': 5.042716232100717e-37, 'Macro_class': 1.0955419207200394e-28}</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.44153665106362106, 'Macro_class': 0.3653457654052022}</t>
+          <t>{'N1ratio-ArgsPreds': -0.4278351922662562, 'Macro_class': 0.36840970543012036}</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.4807058994073272), 'Macro_class': np.float64(0.4130913073140003)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.46649544971383805), 'Macro_class': np.float64(0.41349916830415495)}</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.43991869944543266), 'Macro_class': np.float64(0.3640070050306952)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4260766365141566), 'Macro_class': np.float64(0.3668954096958638)}</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(19.352846212176093), 'Macro_class': np.float64(13.250109971141658)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(18.154130018321673), 'Macro_class': np.float64(13.461224165589575)}</t>
         </is>
       </c>
       <c r="U3" t="n">
-        <v>0.1325010997114161</v>
+        <v>0.1346122416558956</v>
       </c>
       <c r="V3" t="n">
-        <v>135.5928409844293</v>
+        <v>135.9159752579898</v>
       </c>
       <c r="W3" t="n">
-        <v>1.253811974219762e-28</v>
+        <v>1.095541920720843e-28</v>
       </c>
     </row>
     <row r="4">
@@ -726,67 +726,67 @@
         <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3574609078035639</v>
+        <v>0.3489660847113104</v>
       </c>
       <c r="H4" t="n">
-        <v>122.020735231695</v>
+        <v>117.566677837473</v>
       </c>
       <c r="I4" t="n">
-        <v>7.732030001274338e-63</v>
+        <v>5.751093629365206e-61</v>
       </c>
       <c r="J4" t="n">
-        <v>75.5876387960451</v>
+        <v>76.23587479332207</v>
       </c>
       <c r="K4" t="n">
-        <v>117.6389728096677</v>
+        <v>117.0996978851963</v>
       </c>
       <c r="L4" t="n">
-        <v>14.01711133787419</v>
+        <v>13.62127436395809</v>
       </c>
       <c r="M4" t="n">
-        <v>0.114874830997029</v>
+        <v>0.1158599920871156</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1779712145380752</v>
+        <v>0.1771553674511291</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>{'const': 0.4270272555566415, 'N1ratio-ArgsPreds': -2.195768543817306, 'Macro_class': 0.0783461168014444, 'Fam_class': -0.0008073176147426613}</t>
+          <t>{'const': 0.40564951423692774, 'N1ratio-ArgsPreds': -2.0354723429749964, 'Macro_class': 0.07802237381601408, 'Fam_class': -0.000862137100648724}</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>{'const': 6.983427455999342e-11, 'N1ratio-ArgsPreds': 2.7849527092732195e-39, 'Macro_class': 3.944167911357278e-09, 'Fam_class': 0.22591698885923128}</t>
+          <t>{'const': 6.349502533648465e-10, 'N1ratio-ArgsPreds': 6.9646045269335625e-37, 'Macro_class': 5.332337676101321e-09, 'Fam_class': 0.19772957215446743}</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.44013847212347645, 'Macro_class': 0.31410558537744077, 'Fam_class': -0.0638308925158155}</t>
+          <t>{'N1ratio-ArgsPreds': -0.4268328188448389, 'Macro_class': 0.31352708698927223, 'Fam_class': -0.06832199634526862}</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.47969635395302423), 'Macro_class': np.float64(0.22657552294544023), 'Fam_class': np.float64(-0.04719911699693482)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.46598940964904434), 'Macro_class': np.float64(0.22469824786382533), 'Fam_class': np.float64(-0.05020070991952687)}</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.4382293480554767), 'Macro_class': np.float64(0.18646901023729165), 'Fam_class': np.float64(-0.03787633442411308)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.42494967564079716), 'Macro_class': np.float64(0.18605937668379074), 'Fam_class': np.float64(-0.040556418090922676)}</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(19.204496149712813), 'Macro_class': np.float64(3.477069177887518), 'Fam_class': np.float64(0.14346167094072537)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(18.058222682721873), 'Macro_class': np.float64(3.4618091651960734), 'Fam_class': np.float64(0.16448230483657203)}</t>
         </is>
       </c>
       <c r="U4" t="n">
-        <v>0.001434616709407477</v>
+        <v>0.001644823048365662</v>
       </c>
       <c r="V4" t="n">
-        <v>1.469136751762846</v>
+        <v>1.662422710105174</v>
       </c>
       <c r="W4" t="n">
-        <v>0.2259169888597093</v>
+        <v>0.1977295721547984</v>
       </c>
     </row>
     <row r="5">
@@ -811,67 +811,67 @@
         <v>5</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3855974616497843</v>
+        <v>0.3769932747413847</v>
       </c>
       <c r="H5" t="n">
-        <v>82.34078443799439</v>
+        <v>79.39162715384457</v>
       </c>
       <c r="I5" t="n">
-        <v>4.442106470941744e-67</v>
+        <v>4.111853450219204e-65</v>
       </c>
       <c r="J5" t="n">
-        <v>72.27768350317183</v>
+        <v>72.95389930822938</v>
       </c>
       <c r="K5" t="n">
-        <v>117.6389728096677</v>
+        <v>117.0996978851963</v>
       </c>
       <c r="L5" t="n">
-        <v>9.072257861299169</v>
+        <v>8.829159715393393</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1101793955841034</v>
+        <v>0.1112102123601058</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1779712145380752</v>
+        <v>0.1771553674511291</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>{'const': 0.18015827901476222, 'N1ratio-ArgsPreds': -2.0797628700318627, 'Macro_class': 0.06845659271188595, 'Fam_class': -0.0018767080107924884, 'Nlen_freq': 0.28074866988727754, 'Vlen_freq': 0.5450644056063418}</t>
+          <t>{'const': 0.16877812451097274, 'N1ratio-ArgsPreds': -1.9029454343513827, 'Macro_class': 0.06996385328612975, 'Fam_class': -0.0018260318800259777, 'Nlen_freq': 0.13503753454363437, 'Vlen_freq': 0.6579628576506267}</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>{'const': 0.022096224750886184, 'N1ratio-ArgsPreds': 7.7542481976178e-36, 'Macro_class': 2.890193153089037e-07, 'Fam_class': 0.0073492135949451975, 'Nlen_freq': 0.2386491733760133, 'Vlen_freq': 0.013544549634791955}</t>
+          <t>{'const': 0.032912897847550644, 'N1ratio-ArgsPreds': 6.894642942630401e-33, 'Macro_class': 1.7919022379776426e-07, 'Fam_class': 0.009448045664368314, 'Nlen_freq': 0.5678204711671215, 'Vlen_freq': 0.002697369135390786}</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.41688531087324054, 'Macro_class': 0.2744564632502061, 'Fam_class': -0.1483826750871153, 'Nlen_freq': 0.06147936684426154, 'Vlen_freq': 0.12586307125780943}</t>
+          <t>{'N1ratio-ArgsPreds': -0.39904229927534546, 'Macro_class': 0.28114452358334696, 'Fam_class': -0.14470800913173004, 'Nlen_freq': 0.029807946664035818, 'Vlen_freq': 0.15311241881719498}</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.46042737674513745), 'Macro_class': np.float64(0.19839239081483445), 'Fam_class': np.float64(-0.10441310382752554), 'Nlen_freq': np.float64(0.04600078536590982), 'Vlen_freq': np.float64(0.09621588418529682)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.44227506898661123), 'Macro_class': np.float64(0.20177314850356579), 'Fam_class': np.float64(-0.10111212424105663), 'Nlen_freq': np.float64(0.022309849702510036), 'Vlen_freq': np.float64(0.11678445229117221)}</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.40655817977632014), 'Macro_class': np.float64(0.1586613242731975), 'Fam_class': np.float64(-0.08229280502384366), 'Nlen_freq': np.float64(0.03609538954692018), 'Vlen_freq': np.float64(0.07576923079862471)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.3892286042555479), 'Macro_class': np.float64(0.1626055346455999), 'Fam_class': np.float64(-0.08021970641369203), 'Nlen_freq': np.float64(0.01761372126532588), 'Vlen_freq': np.float64(0.09281397296437857)}</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(16.528955354303466), 'Macro_class': np.float64(2.5173415820124734), 'Fam_class': np.float64(0.6772105758692348), 'Nlen_freq': np.float64(0.13028771465439146), 'Vlen_freq': np.float64(0.574097633581526)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(15.149890637072192), 'Macro_class': np.float64(2.644055989738139), 'Fam_class': np.float64(0.6435201297098941), 'Nlen_freq': np.float64(0.03102431768125932), 'Vlen_freq': np.float64(0.8614433577432397)}</t>
         </is>
       </c>
       <c r="U5" t="n">
-        <v>0.02813655384622038</v>
+        <v>0.02802719003007426</v>
       </c>
       <c r="V5" t="n">
-        <v>15.02075444925942</v>
+        <v>14.75572888245837</v>
       </c>
       <c r="W5" t="n">
-        <v>4.183408356918239e-07</v>
+        <v>5.390534006316225e-07</v>
       </c>
     </row>
   </sheetData>

--- a/scripts/checks/results/HLR_results_02_Dunn_fams_tPBC.xlsx
+++ b/scripts/checks/results/HLR_results_02_Dunn_fams_tPBC.xlsx
@@ -562,57 +562,57 @@
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2127090200070492</v>
+        <v>0.2126104794529781</v>
       </c>
       <c r="H2" t="n">
-        <v>178.3177462618833</v>
+        <v>178.2128321208532</v>
       </c>
       <c r="I2" t="n">
-        <v>3.551046890077052e-36</v>
+        <v>3.701627190479354e-36</v>
       </c>
       <c r="J2" t="n">
-        <v>92.1915359049147</v>
+        <v>92.20307497402587</v>
       </c>
       <c r="K2" t="n">
         <v>117.0996978851963</v>
       </c>
       <c r="L2" t="n">
-        <v>24.90816198028165</v>
+        <v>24.89662291117048</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1396841453104768</v>
+        <v>0.139701628748524</v>
       </c>
       <c r="N2" t="n">
         <v>0.1771553674511291</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>{'const': 0.5881292512992626, 'N1ratio-ArgsPreds': -2.1993804205042555}</t>
+          <t>{'const': 0.5877559712647106, 'N1ratio-ArgsPreds': -2.1955128851816026}</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>{'const': 5.747937176790004e-66, 'N1ratio-ArgsPreds': 3.551046890075819e-36}</t>
+          <t>{'const': 5.84595231215245e-66, 'N1ratio-ArgsPreds': 3.701627190478273e-36}</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.4612038811708435}</t>
+          <t>{'N1ratio-ArgsPreds': -0.46109703908502636}</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.4612038811708424)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4610970390850252)}</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.46120388117084227)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.46109703908502514)}</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(21.27090200070484)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(21.26104794529772)}</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -641,67 +641,67 @@
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3473212616629447</v>
+        <v>0.3474892766877657</v>
       </c>
       <c r="H3" t="n">
-        <v>175.3425521559432</v>
+        <v>175.4725440946206</v>
       </c>
       <c r="I3" t="n">
-        <v>8.779581860525752e-62</v>
+        <v>8.065508252607213e-62</v>
       </c>
       <c r="J3" t="n">
-        <v>76.42848307536029</v>
+        <v>76.40880856671357</v>
       </c>
       <c r="K3" t="n">
         <v>117.0996978851963</v>
       </c>
       <c r="L3" t="n">
-        <v>20.33560740491803</v>
+        <v>20.34544465924139</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1159764538321097</v>
+        <v>0.1159465987355289</v>
       </c>
       <c r="N3" t="n">
         <v>0.1771553674511291</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>{'const': 0.33575922902106625, 'N1ratio-ArgsPreds': -2.0402524425515702, 'Macro_class': 0.0916801161601071}</t>
+          <t>{'const': 0.3354116946277601, 'N1ratio-ArgsPreds': -2.037926730489693, 'Macro_class': 0.09176398123990132}</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>{'const': 3.0514726730384744e-20, 'N1ratio-ArgsPreds': 5.042716232100717e-37, 'Macro_class': 1.0955419207200394e-28}</t>
+          <t>{'const': 3.0774548262796214e-20, 'N1ratio-ArgsPreds': 4.6304615366640525e-37, 'Macro_class': 9.648982640828138e-29}</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.4278351922662562, 'Macro_class': 0.36840970543012036}</t>
+          <t>{'N1ratio-ArgsPreds': -0.42800112340187874, 'Macro_class': 0.36874671099508827}</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.46649544971383805), 'Macro_class': np.float64(0.41349916830415495)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.46671126869899615), 'Macro_class': np.float64(0.4138824650594362)}</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.4260766365141566), 'Macro_class': np.float64(0.3668954096958638)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.42627375618027225), 'Macro_class': np.float64(0.3672584883086952)}</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(18.154130018321673), 'Macro_class': np.float64(13.461224165589575)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(18.17093152080382), 'Macro_class': np.float64(13.487879723478798)}</t>
         </is>
       </c>
       <c r="U3" t="n">
-        <v>0.1346122416558956</v>
+        <v>0.1348787972347877</v>
       </c>
       <c r="V3" t="n">
-        <v>135.9159752579898</v>
+        <v>136.2201787681464</v>
       </c>
       <c r="W3" t="n">
-        <v>1.095541920720843e-28</v>
+        <v>9.648982640835361e-29</v>
       </c>
     </row>
     <row r="4">
@@ -726,67 +726,67 @@
         <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3489660847113104</v>
+        <v>0.3490950222132245</v>
       </c>
       <c r="H4" t="n">
-        <v>117.566677837473</v>
+        <v>117.6334142234551</v>
       </c>
       <c r="I4" t="n">
-        <v>5.751093629365206e-61</v>
+        <v>5.38926024134246e-61</v>
       </c>
       <c r="J4" t="n">
-        <v>76.23587479332207</v>
+        <v>76.22077625080185</v>
       </c>
       <c r="K4" t="n">
         <v>117.0996978851963</v>
       </c>
       <c r="L4" t="n">
-        <v>13.62127436395809</v>
+        <v>13.62630721146483</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1158599920871156</v>
+        <v>0.115837045973863</v>
       </c>
       <c r="N4" t="n">
         <v>0.1771553674511291</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>{'const': 0.40564951423692774, 'N1ratio-ArgsPreds': -2.0354723429749964, 'Macro_class': 0.07802237381601408, 'Fam_class': -0.000862137100648724}</t>
+          <t>{'const': 0.4044321491782882, 'N1ratio-ArgsPreds': -2.0329950328383544, 'Macro_class': 0.0782698798845787, 'Fam_class': -0.0008518584602907551}</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>{'const': 6.349502533648465e-10, 'N1ratio-ArgsPreds': 6.9646045269335625e-37, 'Macro_class': 5.332337676101321e-09, 'Fam_class': 0.19772957215446743}</t>
+          <t>{'const': 6.933091660421692e-10, 'N1ratio-ArgsPreds': 6.522930735819514e-37, 'Macro_class': 4.760692740795839e-09, 'Fam_class': 0.20308922670304236}</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.4268328188448389, 'Macro_class': 0.31352708698927223, 'Fam_class': -0.06832199634526862}</t>
+          <t>{'N1ratio-ArgsPreds': -0.4269653785424234, 'Macro_class': 0.3145216716563861, 'Fam_class': -0.06750744233936506}</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.46598940964904434), 'Macro_class': np.float64(0.22469824786382533), 'Fam_class': np.float64(-0.05020070991952687)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4661557404961113), 'Macro_class': np.float64(0.22540611933786894), 'Fam_class': np.float64(-0.049607179321554805)}</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.42494967564079716), 'Macro_class': np.float64(0.18605937668379074), 'Fam_class': np.float64(-0.040556418090922676)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4251013577126499), 'Macro_class': np.float64(0.18665835980530113), 'Fam_class': np.float64(-0.04007175470900394)}</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(18.058222682721873), 'Macro_class': np.float64(3.4618091651960734), 'Fam_class': np.float64(0.16448230483657203)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(18.071116432913833), 'Macro_class': np.float64(3.484134328520525), 'Fam_class': np.float64(0.16057455254585795)}</t>
         </is>
       </c>
       <c r="U4" t="n">
-        <v>0.001644823048365662</v>
+        <v>0.001605745525458779</v>
       </c>
       <c r="V4" t="n">
-        <v>1.662422710105174</v>
+        <v>1.623248541353133</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1977295721547984</v>
+        <v>0.2030892267032514</v>
       </c>
     </row>
     <row r="5">
@@ -811,67 +811,67 @@
         <v>5</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3769932747413847</v>
+        <v>0.3767743170609333</v>
       </c>
       <c r="H5" t="n">
-        <v>79.39162715384457</v>
+        <v>79.31764006463055</v>
       </c>
       <c r="I5" t="n">
-        <v>4.111853450219204e-65</v>
+        <v>4.610175050862416e-65</v>
       </c>
       <c r="J5" t="n">
-        <v>72.95389930822938</v>
+        <v>72.97953918645987</v>
       </c>
       <c r="K5" t="n">
         <v>117.0996978851963</v>
       </c>
       <c r="L5" t="n">
-        <v>8.829159715393393</v>
+        <v>8.824031739747294</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1112102123601058</v>
+        <v>0.1112492975403352</v>
       </c>
       <c r="N5" t="n">
         <v>0.1771553674511291</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>{'const': 0.16877812451097274, 'N1ratio-ArgsPreds': -1.9029454343513827, 'Macro_class': 0.06996385328612975, 'Fam_class': -0.0018260318800259777, 'Nlen_freq': 0.13503753454363437, 'Vlen_freq': 0.6579628576506267}</t>
+          <t>{'const': 0.1692572043035598, 'N1ratio-ArgsPreds': -1.8994373463282095, 'Macro_class': 0.0703072358439516, 'Fam_class': -0.001808172952396705, 'Nlen_freq': 0.13232433524992504, 'Vlen_freq': 0.6562458119930276}</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>{'const': 0.032912897847550644, 'N1ratio-ArgsPreds': 6.894642942630401e-33, 'Macro_class': 1.7919022379776426e-07, 'Fam_class': 0.009448045664368314, 'Nlen_freq': 0.5678204711671215, 'Vlen_freq': 0.002697369135390786}</t>
+          <t>{'const': 0.032396955824896004, 'N1ratio-ArgsPreds': 7.679828348117929e-33, 'Macro_class': 1.5609682226846396e-07, 'Fam_class': 0.010171937807839758, 'Nlen_freq': 0.5806061638562747, 'Vlen_freq': 0.0027840059113080832}</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.39904229927534546, 'Macro_class': 0.28114452358334696, 'Fam_class': -0.14470800913173004, 'Nlen_freq': 0.029807946664035818, 'Vlen_freq': 0.15311241881719498}</t>
+          <t>{'N1ratio-ArgsPreds': -0.39891587165384046, 'Macro_class': 0.2825243807680397, 'Fam_class': -0.143292738187817, 'Nlen_freq': 0.028860824051949313, 'Vlen_freq': 0.15284113890956907}</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.44227506898661123), 'Macro_class': np.float64(0.20177314850356579), 'Fam_class': np.float64(-0.10111212424105663), 'Nlen_freq': np.float64(0.022309849702510036), 'Vlen_freq': np.float64(0.11678445229117221)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4419777356902663), 'Macro_class': np.float64(0.20273820006954038), 'Fam_class': np.float64(-0.10012477268852586), 'Nlen_freq': np.float64(0.021577192080587893), 'Vlen_freq': np.float64(0.11641171137995486)}</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.3892286042555479), 'Macro_class': np.float64(0.1626055346455999), 'Fam_class': np.float64(-0.08021970641369203), 'Nlen_freq': np.float64(0.01761372126532588), 'Vlen_freq': np.float64(0.09281397296437857)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.38897171593413365), 'Macro_class': np.float64(0.1634452212178025), 'Fam_class': np.float64(-0.07944235206898324), 'Nlen_freq': np.float64(0.017038004189102406), 'Vlen_freq': np.float64(0.09252991807777773)}</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(15.149890637072192), 'Macro_class': np.float64(2.644055989738139), 'Fam_class': np.float64(0.6435201297098941), 'Nlen_freq': np.float64(0.03102431768125932), 'Vlen_freq': np.float64(0.8614433577432397)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(15.129899579674436), 'Macro_class': np.float64(2.6714340338936395), 'Fam_class': np.float64(0.6311087302252286), 'Nlen_freq': np.float64(0.029029358674787117), 'Vlen_freq': np.float64(0.8561785739480259)}</t>
         </is>
       </c>
       <c r="U5" t="n">
-        <v>0.02802719003007426</v>
+        <v>0.02767929484770881</v>
       </c>
       <c r="V5" t="n">
-        <v>14.75572888245837</v>
+        <v>14.56744957498187</v>
       </c>
       <c r="W5" t="n">
-        <v>5.390534006316225e-07</v>
+        <v>6.455082394067689e-07</v>
       </c>
     </row>
   </sheetData>
